--- a/output/laminas_comunales/comunal_o_ocup_a_2022_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2022_la_araucania.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,37 +384,37 @@
         </is>
       </c>
       <c r="C2">
-        <v>39.0520927830362</v>
+        <v>59.0107890659427</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C3">
-        <v>36.9153359946773</v>
+        <v>57.6550006553939</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C4">
-        <v>36.9075697488346</v>
+        <v>55.4147755925366</v>
       </c>
     </row>
     <row r="5">
@@ -429,52 +429,52 @@
         </is>
       </c>
       <c r="C5">
-        <v>34.3034351145038</v>
+        <v>53.1363286828518</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="C6">
-        <v>34.0511643902414</v>
+        <v>52.6720106880428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="C7">
-        <v>32.896249514766</v>
+        <v>51.6611751784734</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="C8">
-        <v>32.7241542465105</v>
+        <v>51.3474283033253</v>
       </c>
     </row>
     <row r="9">
@@ -489,202 +489,202 @@
         </is>
       </c>
       <c r="C9">
-        <v>32.2135052139284</v>
+        <v>50.4805996472663</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C10">
-        <v>32.1400441083806</v>
+        <v>50.0898432897372</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="C11">
-        <v>31.0536373878692</v>
+        <v>50.0191101838601</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="C12">
-        <v>31.039009336042</v>
+        <v>49.2233956519671</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="C13">
-        <v>30.2756629922855</v>
+        <v>49.0753045404208</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="C14">
-        <v>29.7044064607182</v>
+        <v>48.6900780379041</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="C15">
-        <v>29.5812752581949</v>
+        <v>48.1955380577428</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="C16">
-        <v>29.0359952581097</v>
+        <v>48.1579167713305</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C17">
-        <v>28.6692058224602</v>
+        <v>47.6362748579545</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="C18">
-        <v>28.4628181181415</v>
+        <v>47.1137324874438</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ercilla</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="C19">
-        <v>27.9284264895776</v>
+        <v>46.970869687588</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="C20">
-        <v>27.550450933119</v>
+        <v>46.876414434432</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C21">
-        <v>27.2917194226386</v>
+        <v>46.7465069860279</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="C22">
-        <v>27.0124908362939</v>
+        <v>46.1404473780711</v>
       </c>
     </row>
     <row r="23">
@@ -699,157 +699,3037 @@
         </is>
       </c>
       <c r="C23">
-        <v>26.6746053144004</v>
+        <v>46.0793415026612</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C24">
-        <v>26.1204026554774</v>
+        <v>45.5567451820128</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="C25">
-        <v>25.4908249747298</v>
+        <v>45.031931657958</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="C26">
-        <v>25.0535610442873</v>
+        <v>44.0639396641403</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="C27">
-        <v>25.0203681072473</v>
+        <v>43.7237565626254</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="C28">
-        <v>24.2019532732857</v>
+        <v>43.5996349759416</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="C29">
-        <v>23.4735861065648</v>
+        <v>43.3696222455404</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="C30">
-        <v>23.0103081795481</v>
+        <v>42.9530965391621</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C31">
-        <v>21.945658626086</v>
+        <v>42.6039559451562</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C32">
-        <v>20.3413162134218</v>
+        <v>42.2720464332522</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>42.0018597811513</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>41.8466223698782</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>41.3108685940392</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>41.2351735823777</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>41.1490442402388</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>40.6584751102709</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>40.6007451102142</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>40.1542111506524</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>39.4387416373015</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>39.4311502938707</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>39.3953177117643</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>39.2592592592593</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>39.2326554161258</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>39.0733657858136</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>39.0520927830362</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>38.701659478032</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>37.8594853683148</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>37.7460419341036</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>37.5762195121951</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>36.9967141538946</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>36.9153359946773</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>36.9075697488346</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>36.8337057133738</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>36.8247487437186</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>36.8026004728132</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>36.6084039548023</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>36.6016131355322</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>36.0827718960539</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>36.0222571811455</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>35.9644080381308</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>35.6833036244801</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>35.4634650142009</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>35.3312467396974</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>35.2470478558111</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>9116</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Saavedra</t>
         </is>
       </c>
-      <c r="C33">
+      <c r="C67">
+        <v>35.1055092241597</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>34.97064456375</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>34.850373589509</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>34.3034351145038</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>34.2147834743654</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>34.0511643902414</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>33.4254209720628</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>33.1307799328914</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>33.1302345058626</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>33.1130420593155</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>33.0162551120774</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>32.896249514766</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>32.8198062792251</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>32.7241542465105</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>32.5398160610139</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>32.4158414702872</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>32.3791910492805</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>32.3476432312331</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>32.2135052139284</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>32.1965699208443</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>32.1560638455229</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>32.1400441083806</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>32.0136228182205</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>31.9390341927905</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>31.8186251560549</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>31.6332899164224</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>31.3632494223519</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>31.2346513461755</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>31.2182372586032</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>31.120915659569</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>31.0536373878692</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>31.039009336042</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>30.8797200520833</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>30.2756629922855</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>30.200225606317</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>30.1536779835391</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>30.0373357228196</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>29.916114790287</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>29.7044064607182</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>29.643158190503</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>29.5961624274877</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>29.5812752581949</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>29.5685809103097</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>29.4899626517274</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>29.4333683105981</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>29.3624362436244</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>29.1229784965346</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>29.0359952581097</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>28.9209039548023</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>28.8982316052669</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>28.889584492673</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>28.7163480296527</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>28.7004914715236</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>28.6692058224602</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>28.4628181181415</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>28.403230184582</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>28.2255310241495</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>27.9284264895776</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>27.7601416478082</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>27.7329649064047</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>27.6849120506938</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>27.6222222222222</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>27.5609534206696</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>27.550450933119</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>27.3552338530067</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>27.2917194226386</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>27.2468096660331</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>27.2387591057523</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>27.0841650033267</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>27.0124908362939</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>26.9646248812915</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>26.9540111363168</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>26.9212882222997</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>26.7793960339011</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>26.6746053144004</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>26.6352086562718</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>26.4786383542112</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>26.2651040247115</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>26.2145262145262</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>26.1204026554774</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>25.7762497837744</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>25.5302882425662</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>25.4908249747298</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>25.3367003367003</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>25.297619047619</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>25.2087605123176</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>25.0535610442873</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>25.0203681072473</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>24.8871181938911</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>24.8397435897436</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>24.7140412501126</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>24.5650048875855</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>24.474358974359</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>24.3804624405355</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>24.2617053264605</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>24.2225570062865</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>24.2019532732857</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>24.0545778336476</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>23.9332404273674</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>23.8727321237994</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>23.7334213338362</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>23.6446173800259</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>23.4735861065648</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>23.3256298713069</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>23.0561755952381</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>23.02524901552</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>23.0103081795481</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>22.7750584903337</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>22.6963718318185</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>22.5972427375677</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>22.3922902494331</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>22.0158450704225</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>21.945658626086</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>21.7268131101813</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>21.6538740596479</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>21.5455217205305</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>21.4275814275814</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>21.0522588868432</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>21.0188152896486</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>20.7035207700101</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>20.3413162134218</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>20.1224226804124</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C189">
         <v>19.8644267609785</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>19.6062479661569</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>19.6033029501127</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>19.3714721586575</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>18.725851773797</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>11.2240801303466</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>10.7068789054083</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>10.5532503457815</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>10.2252571833984</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>9.836229279009389</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>9.634690462911321</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>9.617125093456099</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>9.491129785247431</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>9.439622843672989</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>9.43303714377201</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>8.86593920498831</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>8.82375836836369</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>8.57699805068226</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>8.1780043545218</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>8.15618745255021</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>7.97906863540484</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>7.78575372722253</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>7.60988709854215</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>7.30135658914729</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>7.24672806592341</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>7.0890374615303</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>7.02008858943165</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>6.68638577005111</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>6.60536398467433</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>6.35326018413419</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>5.99682772083943</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>5.84783488466208</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>5.09349593495935</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>4.99015395631937</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>4.43148456716655</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>4.29852320675105</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>3.54479442645472</v>
       </c>
     </row>
   </sheetData>
